--- a/cs.xlsx
+++ b/cs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dastanbaitursynov/Documents/GLOBERCE/oz-fmh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BB903E-6EA3-C349-9D14-B41739A9FCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B09D17F-F9FE-EA40-9E68-D100EE787A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="16800" windowHeight="19740" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="4">
   <si>
     <t>id</t>
   </si>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3371"/>
+  <dimension ref="A1:D3372"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
@@ -27409,6 +27409,14 @@
       </c>
       <c r="B3371" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3372" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3372">
+        <v>5542287</v>
+      </c>
+      <c r="B3372" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
